--- a/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Despliegue.xlsx
+++ b/04_arquitectura/entrega_2/tablas/arquitectura_fisica_Despliegue.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Ambientes de despliegue (RT-" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.1 WAN — tri-camino con SD-WAN" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.3 Segmentación de red (sin so" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2.4 Zero Trust — flujos permiti" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.1 Capa cloud (sa-east-1) — Mu" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3.2 Capa on-premise" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Respaldos — esquema 3-2-1-1-" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Respaldos — esquema 3-2-1-_2" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6. Referencias cruzadas con las" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7. Trazabilidad normativa (resu" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="1. Ambientes de despliegue (RT-" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2.1 WAN — tri-camino con SD-WAN" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="2.3 Segmentación de red (sin so" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="2.4 Zero Trust — flujos permiti" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="3.1 Capa cloud (sa-east-1) — Mu" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="3.2 Capa on-premise" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="5. Respaldos — esquema 3-2-1-1-" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="5. Respaldos — esquema 3-2-1-_2" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="6. Referencias cruzadas con las" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="7. Trazabilidad normativa (resu" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1272,7 +1272,7 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>Excepción: celery-erp-sync → ACL ERP</t>
+          <t>Excepción: erp-sync (trabajador Laravel) → ACL ERP</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
